--- a/output/Table_B_Expansion.xlsx
+++ b/output/Table_B_Expansion.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>GPB_Beta</t>
+          <t>GPGLMM_Beta</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -472,11 +472,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.068601982567156</v>
+        <v>1.06860198256716</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -497,11 +497,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.874957282337633</v>
+        <v>1.87495728233763</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -522,11 +522,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.172456431755374</v>
+        <v>1.17245643175537</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -547,11 +547,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.049328508335033</v>
+        <v>1.04932850833503</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -572,11 +572,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.343081622483382</v>
+        <v>1.34308162248338</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -597,11 +597,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9.805707567512975</v>
+        <v>9.805706481607549</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.462946227719375</v>
+        <v>1.46294622771938</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -647,11 +647,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.649057792495042</v>
+        <v>1.64905779249504</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -672,11 +672,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6560804158098523</v>
+        <v>0.656080415809852</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -697,11 +697,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.213736018318105</v>
+        <v>1.21373601831811</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.6158505813873656</v>
+        <v>0.615850581387366</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -747,11 +747,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.252801009584316</v>
+        <v>1.25280100958432</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -772,11 +772,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.894096862680888</v>
+        <v>1.89409686268089</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.087650003551591</v>
+        <v>1.08765000355159</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -822,11 +822,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.8659636832841301</v>
+        <v>0.86596368328413</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -847,11 +847,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.9500949055675951</v>
+        <v>0.950094905567595</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -922,11 +922,11 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.104524375723355</v>
+        <v>1.10452437572336</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -947,11 +947,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.7738161237531114</v>
+        <v>0.773816123753111</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -972,11 +972,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.8755160853806917</v>
+        <v>0.875516085380692</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -997,11 +997,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.8399166448067772</v>
+        <v>0.839916644806777</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1022,11 +1022,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1.162390352703447</v>
+        <v>1.16239035270345</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1047,11 +1047,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.8456689943776607</v>
+        <v>0.845668994377661</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1072,11 +1072,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-7.361595137842094</v>
+        <v>-7.36159513784198</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1122,11 +1122,11 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.313758211784227</v>
+        <v>1.31375821178423</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.4612292100167147</v>
+        <v>0.461229210016715</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1172,11 +1172,11 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.8737382897568846</v>
+        <v>0.873738289789306</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1222,11 +1222,11 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-0.6945574630192226</v>
+        <v>-0.6945574630192231</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1272,11 +1272,11 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-0.9071060837125637</v>
+        <v>-0.907106083712564</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1297,11 +1297,11 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.7804555223368435</v>
+        <v>0.780455522336843</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.8742204590850755</v>
+        <v>0.874220459085075</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1347,11 +1347,11 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2.310143723812116</v>
+        <v>2.31014372381212</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1397,11 +1397,11 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.4664553561404318</v>
+        <v>0.466455356140432</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1422,11 +1422,11 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.8034289834384318</v>
+        <v>0.8034289834384321</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1447,11 +1447,11 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.5539258473419544</v>
+        <v>0.553925847341954</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1472,11 +1472,11 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.7366181317378289</v>
+        <v>0.736618131737829</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1497,11 +1497,11 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-0.4772884780278904</v>
+        <v>-0.47728847802789</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1522,11 +1522,11 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.3321210803087327</v>
+        <v>0.332121080308733</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.8439758106654529</v>
+        <v>0.843975810665453</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1597,11 +1597,11 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.4333378565400013</v>
+        <v>0.433337856540001</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1647,11 +1647,11 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-0.7848960391308603</v>
+        <v>-0.78489603913086</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1672,11 +1672,11 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-1.116616820294691</v>
+        <v>-1.11661682029469</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
@@ -1697,11 +1697,11 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-0.5572021962846947</v>
+        <v>-0.557202196284695</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>GPGLMM</t>
         </is>
       </c>
     </row>
